--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA64"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7431,6 +7431,103 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>44202</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>5-32 Avenue Gil Ramírez Dávalos</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>http://lataberna.com.ec</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>webtabernas@gmail.com</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4730</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-taberna/</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LATABERNALiquorStore</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lataberna_ec</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LaTabernaEcuador</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AA68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7528,321 @@
       <c r="Z65" s="2" t="inlineStr"/>
       <c r="AA65" s="2" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>46462</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Abelardo J. Andrade</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>010219</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>epesantez@gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4600</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0190072002001</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/gerardo-ortiz-e-hijos/</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ferreteria.gerardoortiz/</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Vega</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>International Purchasing And Product Development Manager</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andres-vega-830b14120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>46462</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Abelardo J. Andrade</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>010219</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>epesantez@gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4600</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0190072002001</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/gerardo-ortiz-e-hijos/</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ferreteria.gerardoortiz/</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Gottifredi</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-gottifredi-037aab1b9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>44202</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>5-32 Avenue Gil Ramírez Dávalos</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>http://lataberna.com.ec</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>webtabernas@gmail.com</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4730</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-taberna/</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LATABERNALiquorStore</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lataberna_ec</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LaTabernaEcuador</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr"/>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA68"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7843,6 +7843,321 @@
       <c r="Z68" s="2" t="inlineStr"/>
       <c r="AA68" s="2" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>46462</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Abelardo J. Andrade</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>010219</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>epesantez@gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4600</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>0190072002001</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/gerardo-ortiz-e-hijos/</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ferreteria.gerardoortiz/</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Andrew Vega</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>International Purchasing And Product Development Manager</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andres-vega-830b14120/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Gerardo Ortiz E Hijos Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>46462</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Abelardo J. Andrade</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>010219</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>epesantez@gerardoortiz.com</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4600</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>0190072002001</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/gerardo-ortiz-e-hijos/</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ferreteria.gerardoortiz/</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Pedro Gottifredi</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pedro-gottifredi-037aab1b9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>La Taberna</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>44202</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Cuenca</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Azuay</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>5-32 Avenue Gil Ramírez Dávalos</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>010101</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>http://lataberna.com.ec</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>webtabernas@gmail.com</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>+593 7-413-4730</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/la-taberna/</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LATABERNALiquorStore</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lataberna_ec</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LaTabernaEcuador</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AA74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8158,6 +8158,309 @@
       <c r="Z71" s="2" t="inlineStr"/>
       <c r="AA71" s="2" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>108161</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>168 Pedro Alarcón</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>170104</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supermercadosantamaria.com</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>comercioelectronico@mega-santamaria.com</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>+593 1800 726 826</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-santa-mar%C3%ADa/</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Supermercados-Santa-Maria-206064130260246</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadossantamaria</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCaY0ZjgFyHW3_rHFNwCZv1A</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Sergio González Noriega</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergio-gonzalez-noriega/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>108161</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>168 Pedro Alarcón</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>170104</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supermercadosantamaria.com</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>comercioelectronico@mega-santamaria.com</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>+593 1800 726 826</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-santa-mar%C3%ADa/</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Supermercados-Santa-Maria-206064130260246</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadossantamaria</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCaY0ZjgFyHW3_rHFNwCZv1A</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Samir Ganum</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>General Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samir-ganum-b1a25410/https://www.linkedin.com/in/samir-ganum-b1a25410/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Santa María</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>108161</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Pichincha, Distrito Metropolitano de Quito</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>168 Pedro Alarcón</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>170104</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.supermercadosantamaria.com</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>comercioelectronico@mega-santamaria.com</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>+593 1800 726 826</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-santa-mar%C3%ADa/</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Supermercados-Santa-Maria-206064130260246</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercadossantamaria</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCaY0ZjgFyHW3_rHFNwCZv1A</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Napoleón Gallardo</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Purchasing</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/napole%C3%B3n-gallardo-b0474b55/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Ecuador.xlsx
+++ b/BWI/bestwine_output/bestwine_Ecuador.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA74"/>
+  <dimension ref="A1:AA77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8461,6 +8461,297 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>46360</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Miravalle 1 Miguel Alemán 151</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>eduardo.sosa@lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>1792796636001</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/importadora-las-vi%C3%B1as/</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CousinoMaculEcuador/</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Javier Díaz</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Founding Partner</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/javier-d%c3%adaz-crespo-9a684b13b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>46360</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Miravalle 1 Miguel Alemán 151</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>eduardo.sosa@lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>1792796636001</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/importadora-las-vi%C3%B1as/</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CousinoMaculEcuador/</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo Sosa Cruz</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eduardo-sosa-cruz-0b840566/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Importadora Las Viiñas Cia. Ltda.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>46360</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Quito</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Urb. Miravalle 1 Miguel Alemán 151</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>eduardo.sosa@lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>1792796636001</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/importadora-las-vi%C3%B1as/</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CousinoMaculEcuador/</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/lasvinas.ec</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>Santiago Garzón Félix</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/santiago-garz%C3%B3n-f%C3%A9lix-67b29014/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
